--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0217.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0217.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Lần đầu hấp thụ Tiếng Vang Hạng Chúa Tể hoặc Hạng Tai Họa.</t>
+          <t>Lần đầu hấp thụ Echo Hạng Chúa Tể hoặc Hạng Tai Họa.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hấp thụ một Tiếng Vang 3 Sao.</t>
+          <t>Hấp thụ một Echo 3 Sao.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hấp thụ một Tiếng Vang 4 Sao.</t>
+          <t>Hấp thụ một Echo 4 Sao.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Tổng cộng hấp thụ 500 Tiếng Vang.</t>
+          <t>Tổng cộng hấp thụ 500 Echo.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Hấp thụ 50 Tiếng Vang 5 Sao.</t>
+          <t>Hấp thụ 50 Echo 5 Sao.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đánh bại Fallacy of Không Return cùng đồng đội trong Chế độ Hợp tác 1 lần.</t>
+          <t>Đánh bại Fallacy of No Return cùng đồng đội trong Chế độ Hợp tác 1 lần.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hoàn thành Tổ Tacet "Độ Sâu Ảo Ảnh" ở bất kỳ độ khó nào cùng Rover: Spectro 1 lần.</t>
+          <t>Hoàn thành Tổ Tacet "Độ Sâu Ảo Ảnh" ở bất kỳ độ khó nào cùng Vận Mệnh Giả: Spectro 1 lần.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào của Dreams Ablaze in Darkness bằng 3 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành bất kỳ độ khó nào của Dreams Ablaze in Darkness bằng 3 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào của Dreams Ablaze in Darkness bằng 5 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành bất kỳ độ khó nào của Dreams Ablaze in Darkness bằng 5 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào của Carnival in Slumberland bằng 3 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành bất kỳ độ khó nào của Carnival in Slumberland bằng 3 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào của Carnival in Slumberland bằng 5 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành bất kỳ độ khó nào của Carnival in Slumberland bằng 5 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Hoàn thành Phantasm Amass ở bất kỳ độ khó nào một lần bằng 3 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành Phantasm Amass ở bất kỳ độ khó nào một lần bằng 3 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Hoàn thành Phantasm Amass ở bất kỳ độ khó nào một lần bằng 5 Cộng Hưởng Giả khác nhau.</t>
+          <t>Hoàn thành Phantasm Amass ở bất kỳ độ khó nào một lần bằng 5 Resonator khác nhau.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Dùng 10 Cộng Hưởng Giả khác nhau để thách đấu bất kỳ độ khó nào của Phantasm Amass</t>
+          <t>Dùng 10 Resonator khác nhau để thách đấu bất kỳ độ khó nào của Phantasm Amass</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
+          <t>Một Resonator bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
+          <t>Một Resonator bí ẩn với khả năng hấp thụ mọi âm thanh. Hiện đang trên hành trình tìm lại ký ức đã mất.</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>L?i ch?o m? ??u?t? ma qu? qu?i lui h?t ?i, m?i ng??i an to?n v? s?!</t>
+          <t>Lời chào mở đầu—Tà ma quỷ quái lui hết đi, mọi người an toàn vô sự!</t>
         </is>
       </c>
     </row>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đủ rồi. R?i ?i.</t>
+          <t>Đủ rồi. Rời đi.</t>
         </is>
       </c>
     </row>
@@ -30476,7 +30476,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>R?i ?i!</t>
+          <t>Rời đi!</t>
         </is>
       </c>
     </row>
